--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.23521521045597</v>
+        <v>4.263222471699095</v>
       </c>
       <c r="D2" t="n">
-        <v>25.00894901558635</v>
+        <v>4.063954215032783</v>
       </c>
       <c r="E2" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F2" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.56224735097267</v>
+        <v>1.716365194533059</v>
       </c>
       <c r="D3" t="n">
-        <v>10.61365252058719</v>
+        <v>1.724718534595419</v>
       </c>
       <c r="E3" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F3" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.86263921551032</v>
+        <v>5.177678872520428</v>
       </c>
       <c r="D4" t="n">
-        <v>31.76189191118464</v>
+        <v>5.161307435567505</v>
       </c>
       <c r="E4" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F4" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.25533937066214</v>
+        <v>7.841492647732599</v>
       </c>
       <c r="D5" t="n">
-        <v>47.99237207908957</v>
+        <v>7.798760462852055</v>
       </c>
       <c r="E5" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F5" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.45734509237209</v>
+        <v>6.899318577510465</v>
       </c>
       <c r="D6" t="n">
-        <v>43.46513289727498</v>
+        <v>7.063084095807185</v>
       </c>
       <c r="E6" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F6" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.59170317331138</v>
+        <v>5.9461517656631</v>
       </c>
       <c r="D7" t="n">
-        <v>37.91119526896882</v>
+        <v>6.160569231207433</v>
       </c>
       <c r="E7" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F7" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.47420316308855</v>
+        <v>4.139558014001889</v>
       </c>
       <c r="D8" t="n">
-        <v>24.84782320345833</v>
+        <v>4.037771270561978</v>
       </c>
       <c r="E8" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F8" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.8974316953267</v>
+        <v>2.420832650490588</v>
       </c>
       <c r="D9" t="n">
-        <v>15.50519401002325</v>
+        <v>2.519594026628778</v>
       </c>
       <c r="E9" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F9" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.24399368278101</v>
+        <v>4.102148973451914</v>
       </c>
       <c r="D10" t="n">
-        <v>5.749303226499975</v>
+        <v>0.9342617743062459</v>
       </c>
       <c r="E10" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F10" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87040685701574</v>
+        <v>4.041441114265058</v>
       </c>
       <c r="D11" t="n">
-        <v>20.72719334120979</v>
+        <v>3.368168917946592</v>
       </c>
       <c r="E11" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F11" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.25270585977881</v>
+        <v>4.591064702214056</v>
       </c>
       <c r="D12" t="n">
-        <v>34.95585399321639</v>
+        <v>5.680326273897663</v>
       </c>
       <c r="E12" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F12" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>26.54868763423036</v>
+        <v>4.314161740562433</v>
       </c>
       <c r="D13" t="n">
-        <v>23.29394919599497</v>
+        <v>3.785266744349183</v>
       </c>
       <c r="E13" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F13" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>21.56584233430988</v>
+        <v>3.504449379325356</v>
       </c>
       <c r="D14" t="n">
-        <v>31.51100144571837</v>
+        <v>5.120537734929236</v>
       </c>
       <c r="E14" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F14" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>10.85326447834827</v>
+        <v>1.763655477731594</v>
       </c>
       <c r="D15" t="n">
-        <v>10.94675796683235</v>
+        <v>1.778848169610257</v>
       </c>
       <c r="E15" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F15" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>19.60082115335518</v>
+        <v>3.185133437420217</v>
       </c>
       <c r="D16" t="n">
-        <v>19.7685760379043</v>
+        <v>3.212393606159449</v>
       </c>
       <c r="E16" t="n">
-        <v>10.23447284069788</v>
+        <v>1.663101836613405</v>
       </c>
       <c r="F16" t="n">
-        <v>11.92150317063592</v>
+        <v>1.937244265228336</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
